--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_020.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_020.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="166">
   <si>
     <t>Sezione</t>
   </si>
@@ -306,6 +306,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -562,11 +568,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.05859375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -3474,39 +3480,39 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>103</v>
@@ -3520,7 +3526,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>104</v>
@@ -3529,7 +3535,7 @@
         <v>12</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>105</v>
@@ -3543,7 +3549,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>106</v>
@@ -3552,7 +3558,7 @@
         <v>12</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>107</v>
@@ -3566,7 +3572,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>108</v>
@@ -3575,7 +3581,7 @@
         <v>12</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>109</v>
@@ -3589,7 +3595,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>110</v>
@@ -3598,10 +3604,10 @@
         <v>12</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3612,19 +3618,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -3635,7 +3641,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>113</v>
@@ -3644,10 +3650,10 @@
         <v>12</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3658,19 +3664,19 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
@@ -3681,7 +3687,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>116</v>
@@ -3690,7 +3696,7 @@
         <v>12</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>117</v>
@@ -3704,7 +3710,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>118</v>
@@ -3713,7 +3719,7 @@
         <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>119</v>
@@ -3727,7 +3733,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>120</v>
@@ -3736,7 +3742,7 @@
         <v>12</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>121</v>
@@ -3750,39 +3756,39 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F139" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>127</v>
@@ -3796,7 +3802,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>128</v>
@@ -3805,7 +3811,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>129</v>
@@ -3819,19 +3825,19 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -3842,16 +3848,16 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>132</v>
@@ -3865,16 +3871,16 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>134</v>
@@ -3888,7 +3894,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>135</v>
@@ -3897,7 +3903,7 @@
         <v>12</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>136</v>
@@ -3911,42 +3917,42 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="C146" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D146" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F146" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -3957,19 +3963,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C148" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
@@ -3980,19 +3986,19 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
@@ -4003,7 +4009,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>141</v>
@@ -4012,7 +4018,7 @@
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>142</v>
@@ -4026,7 +4032,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>143</v>
@@ -4035,7 +4041,7 @@
         <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>144</v>
@@ -4049,7 +4055,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>145</v>
@@ -4058,7 +4064,7 @@
         <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>146</v>
@@ -4072,39 +4078,39 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>152</v>
@@ -4118,7 +4124,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>153</v>
@@ -4127,7 +4133,7 @@
         <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>154</v>
@@ -4141,16 +4147,16 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>156</v>
@@ -4164,16 +4170,16 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>158</v>
@@ -4187,19 +4193,19 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C158" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
@@ -4210,16 +4216,16 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>163</v>
@@ -4228,6 +4234,29 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_020.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_020.xlsx
@@ -41,25 +41,25 @@
     <t>Decreto del Tribunale</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Richiesta di trascrizione</t>
+  </si>
+  <si>
+    <t>Sentenza straniera</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>192.7</t>
+  </si>
+  <si>
     <t>SI</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Richiesta di trascrizione</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Sentenza straniera</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>192.7</t>
   </si>
   <si>
     <t>Si puo' ignorare la sezione per</t>
@@ -646,7 +646,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -666,10 +666,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -686,13 +686,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -738,7 +738,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -761,7 +761,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -784,7 +784,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
@@ -807,7 +807,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -830,7 +830,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>30</v>
@@ -853,7 +853,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>30</v>
@@ -876,7 +876,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>30</v>
@@ -899,7 +899,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>30</v>
@@ -922,7 +922,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>30</v>
@@ -945,7 +945,7 @@
         <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>30</v>
@@ -968,7 +968,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>30</v>
@@ -991,7 +991,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>30</v>
@@ -1014,7 +1014,7 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>30</v>
@@ -1037,7 +1037,7 @@
         <v>49</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -1060,7 +1060,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>30</v>
@@ -1069,7 +1069,7 @@
         <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>32</v>
@@ -1083,7 +1083,7 @@
         <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
@@ -1106,7 +1106,7 @@
         <v>55</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -1115,7 +1115,7 @@
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>32</v>
@@ -1129,7 +1129,7 @@
         <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -1138,7 +1138,7 @@
         <v>58</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>32</v>
@@ -1152,7 +1152,7 @@
         <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -1175,7 +1175,7 @@
         <v>61</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -1198,7 +1198,7 @@
         <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -1221,7 +1221,7 @@
         <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
@@ -1244,7 +1244,7 @@
         <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -1267,7 +1267,7 @@
         <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -1290,7 +1290,7 @@
         <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -1313,7 +1313,7 @@
         <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
@@ -1336,7 +1336,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -1359,7 +1359,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -1382,7 +1382,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -1405,7 +1405,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -1428,7 +1428,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
@@ -1451,7 +1451,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>30</v>
@@ -1474,7 +1474,7 @@
         <v>29</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>88</v>
@@ -1497,7 +1497,7 @@
         <v>33</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>88</v>
@@ -1520,7 +1520,7 @@
         <v>35</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>88</v>
@@ -1543,7 +1543,7 @@
         <v>37</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>88</v>
@@ -1566,7 +1566,7 @@
         <v>39</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>88</v>
@@ -1589,7 +1589,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>88</v>
@@ -1612,7 +1612,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>88</v>
@@ -1635,7 +1635,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>88</v>
@@ -1658,7 +1658,7 @@
         <v>47</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>88</v>
@@ -1681,7 +1681,7 @@
         <v>49</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>88</v>
@@ -1704,7 +1704,7 @@
         <v>51</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>88</v>
@@ -1713,7 +1713,7 @@
         <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>89</v>
@@ -1727,7 +1727,7 @@
         <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>88</v>
@@ -1750,7 +1750,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>88</v>
@@ -1759,7 +1759,7 @@
         <v>56</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>89</v>
@@ -1773,7 +1773,7 @@
         <v>57</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>88</v>
@@ -1782,7 +1782,7 @@
         <v>58</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>89</v>
@@ -1796,7 +1796,7 @@
         <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>88</v>
@@ -1819,7 +1819,7 @@
         <v>61</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>88</v>
@@ -1842,7 +1842,7 @@
         <v>63</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>88</v>
@@ -1865,7 +1865,7 @@
         <v>65</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>88</v>
@@ -1888,7 +1888,7 @@
         <v>67</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>88</v>
@@ -1911,7 +1911,7 @@
         <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>88</v>
@@ -1934,7 +1934,7 @@
         <v>71</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>88</v>
@@ -1957,7 +1957,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>88</v>
@@ -1980,7 +1980,7 @@
         <v>75</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>88</v>
@@ -2003,7 +2003,7 @@
         <v>77</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>88</v>
@@ -2026,7 +2026,7 @@
         <v>79</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>88</v>
@@ -2049,7 +2049,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>88</v>
@@ -2072,7 +2072,7 @@
         <v>83</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>88</v>
@@ -2095,7 +2095,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>88</v>
@@ -2118,7 +2118,7 @@
         <v>90</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>88</v>
@@ -2141,7 +2141,7 @@
         <v>92</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>88</v>
@@ -2164,7 +2164,7 @@
         <v>94</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>88</v>
@@ -2187,7 +2187,7 @@
         <v>96</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>88</v>
@@ -2210,7 +2210,7 @@
         <v>29</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>99</v>
@@ -2233,7 +2233,7 @@
         <v>33</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>99</v>
@@ -2256,7 +2256,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>99</v>
@@ -2279,7 +2279,7 @@
         <v>37</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>99</v>
@@ -2302,7 +2302,7 @@
         <v>39</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>99</v>
@@ -2325,7 +2325,7 @@
         <v>41</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>99</v>
@@ -2348,7 +2348,7 @@
         <v>43</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>99</v>
@@ -2371,7 +2371,7 @@
         <v>45</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>99</v>
@@ -2394,7 +2394,7 @@
         <v>47</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>99</v>
@@ -2417,7 +2417,7 @@
         <v>49</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>99</v>
@@ -2440,7 +2440,7 @@
         <v>51</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>99</v>
@@ -2449,7 +2449,7 @@
         <v>52</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>89</v>
@@ -2463,7 +2463,7 @@
         <v>53</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>99</v>
@@ -2486,7 +2486,7 @@
         <v>55</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>99</v>
@@ -2495,7 +2495,7 @@
         <v>56</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>89</v>
@@ -2509,7 +2509,7 @@
         <v>57</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>99</v>
@@ -2518,7 +2518,7 @@
         <v>58</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>89</v>
@@ -2532,7 +2532,7 @@
         <v>59</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>99</v>
@@ -2555,7 +2555,7 @@
         <v>61</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>99</v>
@@ -2578,7 +2578,7 @@
         <v>63</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>99</v>
@@ -2601,7 +2601,7 @@
         <v>65</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>99</v>
@@ -2624,7 +2624,7 @@
         <v>67</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>99</v>
@@ -2647,7 +2647,7 @@
         <v>69</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>99</v>
@@ -2670,7 +2670,7 @@
         <v>71</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>99</v>
@@ -2693,7 +2693,7 @@
         <v>73</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>99</v>
@@ -2716,7 +2716,7 @@
         <v>75</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>99</v>
@@ -2739,7 +2739,7 @@
         <v>77</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>99</v>
@@ -2762,7 +2762,7 @@
         <v>79</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>99</v>
@@ -2785,7 +2785,7 @@
         <v>81</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>99</v>
@@ -2808,7 +2808,7 @@
         <v>83</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>99</v>
@@ -2831,7 +2831,7 @@
         <v>85</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>99</v>
@@ -2854,7 +2854,7 @@
         <v>90</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>99</v>
@@ -2877,7 +2877,7 @@
         <v>92</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>99</v>
@@ -2900,7 +2900,7 @@
         <v>94</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>99</v>
@@ -2923,7 +2923,7 @@
         <v>96</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>99</v>
@@ -2946,7 +2946,7 @@
         <v>29</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>101</v>
@@ -2969,7 +2969,7 @@
         <v>33</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>101</v>
@@ -2992,7 +2992,7 @@
         <v>35</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>101</v>
@@ -3015,7 +3015,7 @@
         <v>37</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>101</v>
@@ -3038,7 +3038,7 @@
         <v>39</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>101</v>
@@ -3061,7 +3061,7 @@
         <v>41</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>101</v>
@@ -3084,7 +3084,7 @@
         <v>43</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>101</v>
@@ -3107,7 +3107,7 @@
         <v>45</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>101</v>
@@ -3130,7 +3130,7 @@
         <v>47</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>101</v>
@@ -3153,7 +3153,7 @@
         <v>49</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>101</v>
@@ -3176,7 +3176,7 @@
         <v>51</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>101</v>
@@ -3185,7 +3185,7 @@
         <v>52</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>21</v>
@@ -3199,7 +3199,7 @@
         <v>53</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>101</v>
@@ -3222,7 +3222,7 @@
         <v>55</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>101</v>
@@ -3231,7 +3231,7 @@
         <v>56</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>21</v>
@@ -3245,7 +3245,7 @@
         <v>57</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>101</v>
@@ -3254,7 +3254,7 @@
         <v>58</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>21</v>
@@ -3268,7 +3268,7 @@
         <v>59</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>101</v>
@@ -3291,7 +3291,7 @@
         <v>61</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>101</v>
@@ -3314,7 +3314,7 @@
         <v>63</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>101</v>
@@ -3337,7 +3337,7 @@
         <v>65</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>101</v>
@@ -3360,7 +3360,7 @@
         <v>67</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>101</v>
@@ -3383,7 +3383,7 @@
         <v>69</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>101</v>
@@ -3406,7 +3406,7 @@
         <v>71</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>101</v>
@@ -3429,7 +3429,7 @@
         <v>73</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>101</v>
@@ -3452,7 +3452,7 @@
         <v>75</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>101</v>
@@ -3475,7 +3475,7 @@
         <v>77</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>101</v>
@@ -3498,7 +3498,7 @@
         <v>79</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>101</v>
@@ -3521,7 +3521,7 @@
         <v>81</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>101</v>
@@ -3544,7 +3544,7 @@
         <v>83</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>101</v>
@@ -3567,7 +3567,7 @@
         <v>85</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>101</v>
@@ -3590,7 +3590,7 @@
         <v>90</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>101</v>
@@ -3613,7 +3613,7 @@
         <v>92</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>101</v>
@@ -3636,7 +3636,7 @@
         <v>94</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>101</v>
@@ -3659,7 +3659,7 @@
         <v>96</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>101</v>
@@ -3682,7 +3682,7 @@
         <v>102</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>101</v>
@@ -3705,7 +3705,7 @@
         <v>105</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>106</v>
@@ -3728,7 +3728,7 @@
         <v>108</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>106</v>
@@ -3751,7 +3751,7 @@
         <v>110</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>106</v>
@@ -3774,7 +3774,7 @@
         <v>112</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>106</v>
@@ -3797,7 +3797,7 @@
         <v>114</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>106</v>
@@ -3820,7 +3820,7 @@
         <v>116</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>106</v>
@@ -3843,7 +3843,7 @@
         <v>117</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>106</v>
@@ -3866,7 +3866,7 @@
         <v>119</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>106</v>
@@ -3889,7 +3889,7 @@
         <v>120</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>106</v>
@@ -3912,7 +3912,7 @@
         <v>122</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>106</v>
@@ -3935,7 +3935,7 @@
         <v>124</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>106</v>
@@ -3958,7 +3958,7 @@
         <v>126</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>106</v>
@@ -3981,7 +3981,7 @@
         <v>129</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>130</v>
@@ -4004,7 +4004,7 @@
         <v>132</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>130</v>
@@ -4027,7 +4027,7 @@
         <v>134</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>130</v>
@@ -4050,7 +4050,7 @@
         <v>57</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>130</v>
@@ -4073,7 +4073,7 @@
         <v>137</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>130</v>
@@ -4096,7 +4096,7 @@
         <v>139</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>130</v>
@@ -4119,7 +4119,7 @@
         <v>141</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>130</v>
@@ -4142,7 +4142,7 @@
         <v>137</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>144</v>
@@ -4165,7 +4165,7 @@
         <v>141</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>144</v>
@@ -4188,7 +4188,7 @@
         <v>129</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>144</v>
@@ -4211,7 +4211,7 @@
         <v>145</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>144</v>
@@ -4234,7 +4234,7 @@
         <v>147</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>144</v>
@@ -4257,7 +4257,7 @@
         <v>149</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>144</v>
@@ -4280,7 +4280,7 @@
         <v>151</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>144</v>
@@ -4303,7 +4303,7 @@
         <v>154</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>155</v>
@@ -4326,7 +4326,7 @@
         <v>157</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>155</v>
@@ -4349,7 +4349,7 @@
         <v>159</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>155</v>
@@ -4372,7 +4372,7 @@
         <v>161</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>155</v>
@@ -4395,7 +4395,7 @@
         <v>163</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>155</v>
@@ -4418,7 +4418,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>155</v>
@@ -4441,7 +4441,7 @@
         <v>168</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>155</v>
